--- a/data/trans_orig/IP05A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69982</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>80506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74749</t>
+          <t>75617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>136485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152322</t>
+          <t>152713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353295</t>
+          <t>353391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373639</t>
+          <t>373297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417711</t>
+          <t>416927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>437366</t>
+          <t>437953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777483</t>
+          <t>778929</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>806931</t>
+          <t>808521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48753</t>
+          <t>47082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59341</t>
+          <t>57788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86533</t>
+          <t>83278</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24237</t>
+          <t>22692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141049</t>
+          <t>140989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155845</t>
+          <t>155669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132014</t>
+          <t>132466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>144874</t>
+          <t>145063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278569</t>
+          <t>278189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>298060</t>
+          <t>297434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>29022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>573912</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623922</t>
+          <t>624149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>649491</t>
+          <t>649467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1207760</t>
+          <t>1209611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1243799</t>
+          <t>1244863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59322</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77282</t>
+          <t>75692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118058</t>
+          <t>118513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152436</t>
+          <t>152462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80508</t>
+          <t>80347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89023</t>
+          <t>88893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71624</t>
+          <t>71180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>80858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155283</t>
+          <t>155732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167740</t>
+          <t>168226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,47 +3064,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>8509</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>9758</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408897</t>
+          <t>410600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426717</t>
+          <t>427114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442649</t>
+          <t>443277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462847</t>
+          <t>462703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>858444</t>
+          <t>858055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884784</t>
+          <t>885267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41806</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,47 +3407,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>57528</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>45772</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>70066</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>57528</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>45748</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>69947</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145958</t>
+          <t>146323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157980</t>
+          <t>157775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147136</t>
+          <t>147464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>160672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>298498</t>
+          <t>298869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>315580</t>
+          <t>316098</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>646380</t>
+          <t>646724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>667901</t>
+          <t>667802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>670708</t>
+          <t>669975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>696515</t>
+          <t>695515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1325729</t>
+          <t>1325134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1360016</t>
+          <t>1358594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>42003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65675</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76173</t>
+          <t>76023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106923</t>
+          <t>106615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>55785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52291</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103650</t>
+          <t>103046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116619</t>
+          <t>115967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404147</t>
+          <t>403708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426429</t>
+          <t>426143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422461</t>
+          <t>420925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444380</t>
+          <t>443824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>834751</t>
+          <t>833267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>864492</t>
+          <t>865448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49174</t>
+          <t>48445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46694</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87221</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159776</t>
+          <t>159491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167553</t>
+          <t>168075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167100</t>
+          <t>167531</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179014</t>
+          <t>179320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330666</t>
+          <t>330350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>344990</t>
+          <t>345366</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>619370</t>
+          <t>620090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>644709</t>
+          <t>643246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>652796</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>679181</t>
+          <t>678489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1279691</t>
+          <t>1280034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1315677</t>
+          <t>1316402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>53138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>46893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57196</t>
+          <t>57538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96446</t>
+          <t>96341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109101</t>
+          <t>108710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433967</t>
+          <t>433552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447820</t>
+          <t>448056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486708</t>
+          <t>486159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502995</t>
+          <t>503604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926509</t>
+          <t>926340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>947758</t>
+          <t>948567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>25885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39768</t>
+          <t>39385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137944</t>
+          <t>138188</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146170</t>
+          <t>146460</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168837</t>
+          <t>169636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178511</t>
+          <t>178424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>310676</t>
+          <t>310612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323103</t>
+          <t>323170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>625845</t>
+          <t>625985</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>643683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>711773</t>
+          <t>711808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>734682</t>
+          <t>734022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1345484</t>
+          <t>1344876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1372326</t>
+          <t>1373396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,82 +8507,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16972</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17143</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>27136</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>18039</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>11517</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69519</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63156</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74878</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>75818</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>69786</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80506</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>69722</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80534</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69519</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63195</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75617</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136485</t>
+          <t>136775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20429</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12497</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7623</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18235</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7984</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18033</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13896</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20186</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4338</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3430</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89562</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>89562</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>89562</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>428811</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>417738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>438823</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>552</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>364693</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>353391</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>373297</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>353212</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>374083</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>428811</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>416927</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>437953</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778929</t>
+          <t>778802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808521</t>
+          <t>807495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>34162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25218</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44185</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>37557</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28936</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>47082</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>29177</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>48483</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>34162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>25221</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>44715</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57788</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83278</t>
+          <t>85588</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -1410,67 +1410,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7919</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>7976</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4572</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14174</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7919</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4375</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13772</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>470892</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>470892</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>470892</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>410226</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>410226</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>410226</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>470892</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>470892</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>470892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139034</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>130776</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>144387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>149185</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>140989</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>155669</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>140499</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>155507</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>86,47%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139034</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132466</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>145063</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278189</t>
+          <t>278006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>297434</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15121</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22928</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21113</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14777</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29022</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14936</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29468</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15121</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9724</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21174</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45783</t>
+          <t>46402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7973</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2222</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6396</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7212</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157453</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157453</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157453</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157453</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157453</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>637364</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>623205</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>650479</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>883</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>589695</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>574508</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>603460</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>576160</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>604994</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>87,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>637364</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>624149</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>649467</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1209611</t>
+          <t>1207279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1244863</t>
+          <t>1245334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -2204,74 +2204,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63180</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51117</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>76606</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>71167</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58701</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>84795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>57683</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>84773</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>12,61%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>63180</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52148</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>201</t>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118513</t>
+          <t>119046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152462</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14646</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9292</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21933</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11445</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6723</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17251</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>14646</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9645</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>21662</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>715190</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>715190</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>715190</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>672307</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>672307</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>672307</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>715190</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>715190</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>715190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76724</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71243</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80718</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>82,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85772</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>80347</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88893</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>80136</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>88783</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>76724</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71180</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80858</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155732</t>
+          <t>155536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168226</t>
+          <t>167918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4366</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9822</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8983</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6718</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11388</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1463</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4827</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2750</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7074</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>453419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>443884</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>463283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>607</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>419324</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>410600</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>427114</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>410046</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>427056</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>453419</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>443277</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>462703</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>858055</t>
+          <t>857737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885267</t>
+          <t>885706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32328</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23356</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40890</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>25199</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>17743</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33538</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18090</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33570</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>5,6%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>32328</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>23815</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41675</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>46302</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70066</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5066</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9962</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7052</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12718</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18715</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>492800</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>492800</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>492800</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>449589</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>449589</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>449589</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>492800</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>492800</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>492800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>154873</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>147681</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160718</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152847</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146323</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>157775</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>145922</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>157636</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>154873</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>147464</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160672</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>298869</t>
+          <t>298472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>316098</t>
+          <t>316238</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13797</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8614</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20985</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8362</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14082</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14305</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13797</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8796</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21390</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5602</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10636</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170872</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170872</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170872</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>685016</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>669548</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>696149</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>948</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>657944</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>646724</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>667802</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>645741</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>668756</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>92,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>685016</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>669975</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>695515</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1325134</t>
+          <t>1324705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1358594</t>
+          <t>1357749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>52844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>66818</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37928</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29497</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>47842</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28275</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>48866</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>52844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42003</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>65814</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106615</t>
+          <t>106912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -4377,67 +4377,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>12004</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18699</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>12130</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7250</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18993</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12004</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7028</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>18877</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>749864</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>749864</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>749864</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>708002</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>708002</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>708002</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>749864</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>749864</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>749864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57855</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52395</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61944</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>52611</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47737</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55785</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47907</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>55868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>89,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57855</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51866</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62020</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103046</t>
+          <t>104105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115967</t>
+          <t>116192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9531</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2512</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6271</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6395</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10190</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5283</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3627</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7517</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,17%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5283</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9412</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58750</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>434079</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>421368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>444933</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>415794</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>403708</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>426143</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>403446</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>425499</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>434079</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>420925</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>443824</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>833267</t>
+          <t>833407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>865448</t>
+          <t>864164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36670</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28351</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>48070</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>38186</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>29672</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48445</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>29465</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>47760</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36670</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>28123</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>46680</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87888</t>
+          <t>89218</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15670</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9974</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22673</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15368</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10147</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22353</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10800</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21837</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15670</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10275</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23437</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>486419</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>486419</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>486419</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>486419</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>486419</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>486419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>174360</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166787</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>178802</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>164556</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>159491</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>168075</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>159794</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>167797</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>95,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>174360</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>167531</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>179320</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>331133</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>345366</t>
+          <t>345078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10515</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6387</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18157</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5083</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9419</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10515</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17040</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5976,67 +5976,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1862</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186732</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186732</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186732</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171501</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171501</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171501</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186732</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186732</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>666294</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>651478</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>678659</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>948</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>632960</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>620090</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>643246</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>619998</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>645554</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>90,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>666294</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>651138</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>678489</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>89,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1280034</t>
+          <t>1279349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1316402</t>
+          <t>1316267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>52661</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42024</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>65883</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>45780</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>36739</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56323</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>35881</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57097</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>6,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>52661</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42609</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>64958</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82953</t>
+          <t>84046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115230</t>
+          <t>115171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22810</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16678</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31302</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20856</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14896</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>28885</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>22810</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16306</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>31218</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54957</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>741764</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>741764</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>741764</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>699597</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>699597</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>699597</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>741764</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>741764</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>741764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>48406</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42789</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52104</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50692</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46657</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53138</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53204</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46893</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57538</t>
+          <t>45107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103896</t>
+          <t>90943</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>83811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108710</t>
+          <t>95859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7678</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5572</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10268</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5406</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10513</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>456808</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>446582</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>463374</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>614</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>441867</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>433552</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>448056</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496133</t>
+          <t>413410</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486159</t>
+          <t>405193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503604</t>
+          <t>419351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>938001</t>
+          <t>870219</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926340</t>
+          <t>856804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948567</t>
+          <t>879281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -7457,62 +7457,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15157</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9244</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25383</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>13126</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19149</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10395</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>976412</t>
+          <t>907375</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>976412</t>
+          <t>907375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976412</t>
+          <t>907375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>160843</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155614</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163879</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>143006</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>138188</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146460</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>174981</t>
+          <t>143150</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169636</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178424</t>
+          <t>146396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>317986</t>
+          <t>303993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>310612</t>
+          <t>297335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323170</t>
+          <t>309000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149108</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149108</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>149592</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>149592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>149592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>330436</t>
+          <t>316110</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>330436</t>
+          <t>316110</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>330436</t>
+          <t>316110</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>666057</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>654316</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>675658</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>635566</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>625985</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>643683</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>724318</t>
+          <t>599096</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>711808</t>
+          <t>589999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>734022</t>
+          <t>607336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1359883</t>
+          <t>1265153</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1344876</t>
+          <t>1250249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1373396</t>
+          <t>1276597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23390</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15781</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>19177</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13181</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26577</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57244</t>
+          <t>56132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8953</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8406</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15657</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>27222</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>698401</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>698401</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>698401</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>663149</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>663149</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>663149</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>759427</t>
+          <t>627677</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>759427</t>
+          <t>627677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>759427</t>
+          <t>627677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1422575</t>
+          <t>1326078</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1422575</t>
+          <t>1326078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1422575</t>
+          <t>1326078</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
